--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230971</v>
+        <v>113230972</v>
       </c>
       <c r="B2" t="n">
-        <v>99554</v>
+        <v>99570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548594</v>
+        <v>548617</v>
       </c>
       <c r="R2" t="n">
-        <v>6626393</v>
+        <v>6626368</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113230973</v>
+        <v>113230971</v>
       </c>
       <c r="B3" t="n">
-        <v>99554</v>
+        <v>99570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548623</v>
+        <v>548594</v>
       </c>
       <c r="R3" t="n">
-        <v>6626376</v>
+        <v>6626393</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230972</v>
+        <v>113230973</v>
       </c>
       <c r="B4" t="n">
-        <v>99554</v>
+        <v>99570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548617</v>
+        <v>548623</v>
       </c>
       <c r="R4" t="n">
-        <v>6626368</v>
+        <v>6626376</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113230971</v>
+        <v>113230973</v>
       </c>
       <c r="B3" t="n">
         <v>99570</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548594</v>
+        <v>548623</v>
       </c>
       <c r="R3" t="n">
-        <v>6626393</v>
+        <v>6626376</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230973</v>
+        <v>113230971</v>
       </c>
       <c r="B4" t="n">
         <v>99570</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548623</v>
+        <v>548594</v>
       </c>
       <c r="R4" t="n">
-        <v>6626376</v>
+        <v>6626393</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230972</v>
+        <v>113230971</v>
       </c>
       <c r="B2" t="n">
-        <v>99570</v>
+        <v>99582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548617</v>
+        <v>548594</v>
       </c>
       <c r="R2" t="n">
-        <v>6626368</v>
+        <v>6626393</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -780,7 +780,7 @@
         <v>113230973</v>
       </c>
       <c r="B3" t="n">
-        <v>99570</v>
+        <v>99582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230971</v>
+        <v>113230972</v>
       </c>
       <c r="B4" t="n">
-        <v>99570</v>
+        <v>99582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548594</v>
+        <v>548617</v>
       </c>
       <c r="R4" t="n">
-        <v>6626393</v>
+        <v>6626368</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230971</v>
+        <v>113230973</v>
       </c>
       <c r="B2" t="n">
         <v>99582</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548594</v>
+        <v>548623</v>
       </c>
       <c r="R2" t="n">
-        <v>6626393</v>
+        <v>6626376</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113230973</v>
+        <v>113230971</v>
       </c>
       <c r="B3" t="n">
         <v>99582</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548623</v>
+        <v>548594</v>
       </c>
       <c r="R3" t="n">
-        <v>6626376</v>
+        <v>6626393</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230973</v>
+        <v>113230972</v>
       </c>
       <c r="B2" t="n">
-        <v>99582</v>
+        <v>99604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548623</v>
+        <v>548617</v>
       </c>
       <c r="R2" t="n">
-        <v>6626376</v>
+        <v>6626368</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -780,7 +780,7 @@
         <v>113230971</v>
       </c>
       <c r="B3" t="n">
-        <v>99582</v>
+        <v>99604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230972</v>
+        <v>113230973</v>
       </c>
       <c r="B4" t="n">
-        <v>99582</v>
+        <v>99604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548617</v>
+        <v>548623</v>
       </c>
       <c r="R4" t="n">
-        <v>6626368</v>
+        <v>6626376</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113230972</v>
       </c>
       <c r="B2" t="n">
-        <v>99604</v>
+        <v>99608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113230971</v>
       </c>
       <c r="B3" t="n">
-        <v>99604</v>
+        <v>99608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113230973</v>
       </c>
       <c r="B4" t="n">
-        <v>99604</v>
+        <v>99608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230972</v>
+        <v>113230971</v>
       </c>
       <c r="B2" t="n">
-        <v>99608</v>
+        <v>99614</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548617</v>
+        <v>548594</v>
       </c>
       <c r="R2" t="n">
-        <v>6626368</v>
+        <v>6626393</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113230971</v>
+        <v>113230973</v>
       </c>
       <c r="B3" t="n">
-        <v>99608</v>
+        <v>99614</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548594</v>
+        <v>548623</v>
       </c>
       <c r="R3" t="n">
-        <v>6626393</v>
+        <v>6626376</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230973</v>
+        <v>113230972</v>
       </c>
       <c r="B4" t="n">
-        <v>99608</v>
+        <v>99614</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548623</v>
+        <v>548617</v>
       </c>
       <c r="R4" t="n">
-        <v>6626376</v>
+        <v>6626368</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230971</v>
+        <v>113230972</v>
       </c>
       <c r="B2" t="n">
         <v>99614</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548594</v>
+        <v>548617</v>
       </c>
       <c r="R2" t="n">
-        <v>6626393</v>
+        <v>6626368</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230972</v>
+        <v>113230971</v>
       </c>
       <c r="B4" t="n">
         <v>99614</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548617</v>
+        <v>548594</v>
       </c>
       <c r="R4" t="n">
-        <v>6626368</v>
+        <v>6626393</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132807644</v>
       </c>
       <c r="B5" t="n">
-        <v>58090</v>
+        <v>58097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132807644</v>
       </c>
       <c r="B5" t="n">
-        <v>58097</v>
+        <v>58107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61212-2022 artfynd.xlsx
+++ b/artfynd/A 61212-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113230971</v>
+        <v>73458710</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Färna herrgård, Vstm</t>
+          <t>Färna, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548595</v>
+        <v>548571</v>
       </c>
       <c r="R2" t="n">
-        <v>6626392</v>
+        <v>6626164</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,71 +764,77 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Sluttning ner mot Lillsjön med gammal tall, grov asp och yngre gallrings-granskog.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Wiberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Wiberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113230973</v>
+        <v>113145182</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Färna herrgård, Vstm</t>
+          <t>Färna herrgård, S om, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548623</v>
+        <v>548516</v>
       </c>
       <c r="R3" t="n">
-        <v>6626376</v>
+        <v>6626358</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,69 +874,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Park och blandad skog nära vatten</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113230972</v>
+        <v>113145184</v>
       </c>
       <c r="B4" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Färna herrgård, Vstm</t>
+          <t>Färna herrgård, S om, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548617</v>
+        <v>548516</v>
       </c>
       <c r="R4" t="n">
-        <v>6626368</v>
+        <v>6626358</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,26 +976,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Park och blandad skog nära vatten</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132807644</v>
+        <v>113230968</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,41 +1008,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205976</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flata stenen, Flata stenen, Vstm</t>
+          <t>Färna herrgård, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548603</v>
+        <v>548580</v>
       </c>
       <c r="R5" t="n">
-        <v>6626413</v>
+        <v>6626313</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1050,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,15 +1082,601 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113230969</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Färna herrgård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548564</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626235</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113230967</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Färna herrgård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>548490</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626373</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132807644</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flata stenen, Flata stenen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548603</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626413</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Per Appeltofft</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Per Appeltofft</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113230971</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Färna herrgård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>548595</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626392</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113230972</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Färna herrgård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>548617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113230973</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Färna herrgård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>548623</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626376</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
